--- a/solvvision/solvvision-mcp-findings.xlsx
+++ b/solvvision/solvvision-mcp-findings.xlsx
@@ -7,11 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Findings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Legend" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Legend" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Findings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Future Features" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Findings'!$A$1:$M$274</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Findings'!$A$1:$M$274</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Future Features'!$A$1:$F$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,8 +51,12 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -97,6 +103,24 @@
         <fgColor rgb="00EBF3FB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEEFF"/>
+        <bgColor rgb="00DDEEFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -138,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -184,6 +208,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -550,6 +583,414 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Tool returned real ServiceNow data with expected shape</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Tool errored, threw, or returned HTTP error</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Fishy</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Tool returned 200 but suspicious output (wrong data, silent state mismatch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Pre-condition not met — plugin missing, flag off, guard blocked call</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Root Cause Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Wrong table name</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Implementation references a non-existent ServiceNow table</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Workflow gate</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>ServiceNow Business Rule blocks direct Table API state transition</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Broken round-trip</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Tool A creates a record, Tool B cannot operate on it using the returned ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Silent lie</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Tool returns HTTP 200 success but the intended change did not happen</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>PDI config</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Requires PDI setup not present on a standard free PDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Misleading name</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Tool name implies broader capability than the implementation delivers</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Now Assist guard — genuine</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Tool legitimately requires Now Assist plugin (nlq_query, ai_search, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Now Assist guard — spurious</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Plain Table API tool incorrectly blocked because requireNowAssist() is called at the top of executeNowAssistToolCall() before the switch, blocking all tools dispatched to that handler</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Fix Complexity</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Table name fix or guard removal — straightforward code change, verifiable in minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Needs investigation before fixing (source dive, PDI verification, or API research required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Touches workflow engine, plugin dependency, or requires non-trivial ServiceNow API research</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Upstream or Fork Fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Fork</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>Fix stays in Solvvision fork only — not suitable for upstream PR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>Upstream</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Worth raising as PR or issue to aartiq/servicenow-mcp — affects all users</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>Not yet actioned</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Fix being actively worked on</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>Fix committed to fork</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>Wont Fix</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Accepted as-is and documented</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Phase Discovered</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>Found during 30-prompt manual checklist run (2026-05-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>Found during automated full-coverage harness run (2026-05-04)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1897,9 +2338,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K21" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -1909,7 +2350,7 @@
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -1960,9 +2401,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K22" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
@@ -1972,7 +2413,7 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -2023,9 +2464,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K23" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -2035,7 +2476,7 @@
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -2086,9 +2527,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K24" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L24" s="7" t="inlineStr">
@@ -2098,7 +2539,7 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -2149,9 +2590,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K25" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -2161,7 +2602,7 @@
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -2212,9 +2653,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K26" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L26" s="7" t="inlineStr">
@@ -2224,7 +2665,7 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -2275,9 +2716,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K27" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -2287,7 +2728,7 @@
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -2338,9 +2779,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K28" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr">
@@ -2350,7 +2791,7 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -2401,9 +2842,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K29" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -2413,7 +2854,7 @@
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -2464,9 +2905,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K30" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
@@ -2476,7 +2917,7 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -2527,9 +2968,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K31" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
@@ -2539,7 +2980,7 @@
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -2590,9 +3031,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K32" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
@@ -2602,7 +3043,7 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -2653,9 +3094,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K33" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
@@ -2665,7 +3106,7 @@
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -2716,9 +3157,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K34" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
@@ -2728,7 +3169,7 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -2779,9 +3220,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K35" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
@@ -2791,7 +3232,7 @@
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -2842,9 +3283,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K36" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
@@ -2854,7 +3295,7 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -2905,9 +3346,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K37" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
@@ -2917,7 +3358,7 @@
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -2968,9 +3409,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K38" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
@@ -2980,7 +3421,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -3031,9 +3472,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K39" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -3043,7 +3484,7 @@
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -3094,9 +3535,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K40" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
@@ -3106,7 +3547,7 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -3157,9 +3598,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K41" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
@@ -3169,7 +3610,7 @@
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -3220,9 +3661,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K42" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
@@ -3232,7 +3673,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -3283,9 +3724,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K43" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -3295,7 +3736,7 @@
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -3346,9 +3787,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K44" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
@@ -3358,7 +3799,7 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -3409,9 +3850,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K45" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
@@ -3421,7 +3862,7 @@
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -3472,9 +3913,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K46" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
@@ -3484,7 +3925,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -3535,9 +3976,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K47" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -3547,7 +3988,7 @@
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -3598,9 +4039,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K48" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
@@ -3610,7 +4051,7 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -3661,9 +4102,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K49" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
@@ -3673,7 +4114,7 @@
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -3724,9 +4165,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K50" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
@@ -3736,7 +4177,7 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -3787,9 +4228,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K51" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
@@ -3799,7 +4240,7 @@
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -3850,9 +4291,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K52" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
@@ -3862,7 +4303,7 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -3913,9 +4354,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K53" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
@@ -3925,7 +4366,7 @@
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -3976,9 +4417,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K54" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
@@ -3988,7 +4429,7 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -4039,9 +4480,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K55" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
@@ -4051,7 +4492,7 @@
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -4102,9 +4543,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K56" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
@@ -4114,7 +4555,7 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -4165,9 +4606,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K57" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
@@ -4177,7 +4618,7 @@
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -4228,9 +4669,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K58" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -4240,7 +4681,7 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -4291,9 +4732,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K59" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K59" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
@@ -4303,7 +4744,7 @@
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -4354,9 +4795,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K60" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
@@ -4366,7 +4807,7 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -4417,9 +4858,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K61" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K61" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
@@ -4429,7 +4870,7 @@
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -4480,9 +4921,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K62" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
@@ -4492,7 +4933,7 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -4543,9 +4984,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K63" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K63" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
@@ -4555,7 +4996,7 @@
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -4606,9 +5047,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K64" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
@@ -4618,7 +5059,7 @@
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -4669,9 +5110,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K65" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K65" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
@@ -4681,7 +5122,7 @@
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -4732,9 +5173,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K66" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
@@ -4744,7 +5185,7 @@
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -4795,9 +5236,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K67" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K67" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
@@ -4807,7 +5248,7 @@
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -4858,9 +5299,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K68" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
@@ -4870,7 +5311,7 @@
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -4921,9 +5362,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K69" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K69" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -4933,7 +5374,7 @@
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -4984,9 +5425,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K70" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
@@ -4996,7 +5437,7 @@
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -5047,9 +5488,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K71" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K71" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
@@ -5059,7 +5500,7 @@
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -5110,9 +5551,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K72" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
@@ -5122,7 +5563,7 @@
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -5173,9 +5614,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K73" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K73" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
@@ -5185,7 +5626,7 @@
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -5236,9 +5677,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K74" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
@@ -5248,7 +5689,7 @@
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -5299,9 +5740,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K75" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K75" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
@@ -5311,7 +5752,7 @@
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -5362,9 +5803,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K76" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L76" s="7" t="inlineStr">
@@ -5374,7 +5815,7 @@
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -5425,9 +5866,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K77" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K77" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
@@ -5437,7 +5878,7 @@
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -5488,9 +5929,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K78" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L78" s="7" t="inlineStr">
@@ -5500,7 +5941,7 @@
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -5551,9 +5992,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K79" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K79" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
@@ -5563,7 +6004,7 @@
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -5614,9 +6055,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K80" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L80" s="7" t="inlineStr">
@@ -5626,7 +6067,7 @@
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -5677,9 +6118,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K81" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K81" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
@@ -5689,7 +6130,7 @@
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -5740,9 +6181,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K82" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L82" s="7" t="inlineStr">
@@ -5752,7 +6193,7 @@
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -5803,9 +6244,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K83" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K83" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
@@ -5815,7 +6256,7 @@
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -5866,9 +6307,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K84" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L84" s="7" t="inlineStr">
@@ -5878,7 +6319,7 @@
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -5929,9 +6370,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K85" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K85" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
@@ -5941,7 +6382,7 @@
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -5992,9 +6433,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K86" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L86" s="7" t="inlineStr">
@@ -6004,7 +6445,7 @@
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -6055,9 +6496,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K87" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K87" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
@@ -6067,7 +6508,7 @@
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -6118,9 +6559,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K88" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L88" s="7" t="inlineStr">
@@ -6130,7 +6571,7 @@
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -6181,9 +6622,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K89" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K89" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
@@ -6193,7 +6634,7 @@
       </c>
       <c r="M89" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -6244,9 +6685,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K90" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L90" s="7" t="inlineStr">
@@ -6256,7 +6697,7 @@
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -6307,9 +6748,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K91" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K91" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
@@ -6319,7 +6760,7 @@
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -6370,9 +6811,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K92" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
@@ -6382,7 +6823,7 @@
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -6433,9 +6874,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K93" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K93" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
@@ -6445,7 +6886,7 @@
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -6496,9 +6937,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K94" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L94" s="7" t="inlineStr">
@@ -6508,7 +6949,7 @@
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -6559,9 +7000,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K95" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K95" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
@@ -6571,7 +7012,7 @@
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -6622,9 +7063,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K96" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L96" s="7" t="inlineStr">
@@ -6634,7 +7075,7 @@
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -6685,9 +7126,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K97" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K97" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
@@ -6697,7 +7138,7 @@
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -6748,9 +7189,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K98" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L98" s="7" t="inlineStr">
@@ -6760,7 +7201,7 @@
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -6811,9 +7252,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K99" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K99" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
@@ -6823,7 +7264,7 @@
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -6874,9 +7315,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K100" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L100" s="7" t="inlineStr">
@@ -6886,7 +7327,7 @@
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -6937,9 +7378,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K101" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K101" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
@@ -6949,7 +7390,7 @@
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -7000,9 +7441,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K102" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L102" s="7" t="inlineStr">
@@ -7012,7 +7453,7 @@
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -7063,9 +7504,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K103" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K103" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L103" s="7" t="inlineStr">
@@ -7075,7 +7516,7 @@
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -7126,9 +7567,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K104" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L104" s="7" t="inlineStr">
@@ -7138,7 +7579,7 @@
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -7189,9 +7630,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K105" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K105" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L105" s="7" t="inlineStr">
@@ -7201,7 +7642,7 @@
       </c>
       <c r="M105" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -7252,9 +7693,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K106" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L106" s="7" t="inlineStr">
@@ -7264,7 +7705,7 @@
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -7315,9 +7756,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K107" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K107" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L107" s="7" t="inlineStr">
@@ -7327,7 +7768,7 @@
       </c>
       <c r="M107" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -7378,9 +7819,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K108" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K108" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L108" s="7" t="inlineStr">
@@ -7390,7 +7831,7 @@
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -7441,9 +7882,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K109" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K109" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L109" s="7" t="inlineStr">
@@ -7453,7 +7894,7 @@
       </c>
       <c r="M109" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -7504,9 +7945,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K110" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K110" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L110" s="7" t="inlineStr">
@@ -7516,7 +7957,7 @@
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -7567,9 +8008,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K111" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K111" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L111" s="7" t="inlineStr">
@@ -7579,7 +8020,7 @@
       </c>
       <c r="M111" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -7630,9 +8071,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K112" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L112" s="7" t="inlineStr">
@@ -7642,7 +8083,7 @@
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -7693,9 +8134,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K113" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K113" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L113" s="7" t="inlineStr">
@@ -7705,7 +8146,7 @@
       </c>
       <c r="M113" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -7756,9 +8197,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K114" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L114" s="7" t="inlineStr">
@@ -7768,7 +8209,7 @@
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -7819,9 +8260,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K115" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K115" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L115" s="7" t="inlineStr">
@@ -7831,7 +8272,7 @@
       </c>
       <c r="M115" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -7882,9 +8323,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K116" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K116" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L116" s="7" t="inlineStr">
@@ -7894,7 +8335,7 @@
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -7945,9 +8386,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K117" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K117" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L117" s="7" t="inlineStr">
@@ -7957,7 +8398,7 @@
       </c>
       <c r="M117" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -8008,9 +8449,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K118" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K118" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L118" s="7" t="inlineStr">
@@ -8020,7 +8461,7 @@
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -8071,9 +8512,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K119" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K119" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L119" s="7" t="inlineStr">
@@ -8083,7 +8524,7 @@
       </c>
       <c r="M119" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -8134,9 +8575,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K120" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K120" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L120" s="7" t="inlineStr">
@@ -8146,7 +8587,7 @@
       </c>
       <c r="M120" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -8197,9 +8638,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K121" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K121" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L121" s="7" t="inlineStr">
@@ -8209,7 +8650,7 @@
       </c>
       <c r="M121" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -8260,9 +8701,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K122" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K122" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L122" s="7" t="inlineStr">
@@ -8272,7 +8713,7 @@
       </c>
       <c r="M122" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -8323,9 +8764,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K123" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K123" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L123" s="7" t="inlineStr">
@@ -8335,7 +8776,7 @@
       </c>
       <c r="M123" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -8386,9 +8827,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K124" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K124" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L124" s="7" t="inlineStr">
@@ -8398,7 +8839,7 @@
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -8449,9 +8890,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K125" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K125" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L125" s="7" t="inlineStr">
@@ -8461,7 +8902,7 @@
       </c>
       <c r="M125" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -8512,9 +8953,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K126" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K126" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L126" s="7" t="inlineStr">
@@ -8524,7 +8965,7 @@
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -8575,9 +9016,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K127" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K127" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L127" s="7" t="inlineStr">
@@ -8587,7 +9028,7 @@
       </c>
       <c r="M127" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -8638,9 +9079,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K128" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K128" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L128" s="7" t="inlineStr">
@@ -8650,7 +9091,7 @@
       </c>
       <c r="M128" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -8701,9 +9142,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K129" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K129" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L129" s="7" t="inlineStr">
@@ -8713,7 +9154,7 @@
       </c>
       <c r="M129" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -8764,9 +9205,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K130" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K130" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L130" s="7" t="inlineStr">
@@ -8776,7 +9217,7 @@
       </c>
       <c r="M130" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -8827,9 +9268,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K131" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K131" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L131" s="7" t="inlineStr">
@@ -8839,7 +9280,7 @@
       </c>
       <c r="M131" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -8890,9 +9331,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K132" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K132" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L132" s="7" t="inlineStr">
@@ -8902,7 +9343,7 @@
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -8953,9 +9394,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K133" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K133" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L133" s="7" t="inlineStr">
@@ -8965,7 +9406,7 @@
       </c>
       <c r="M133" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -9016,9 +9457,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K134" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K134" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L134" s="7" t="inlineStr">
@@ -9028,7 +9469,7 @@
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -9079,9 +9520,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K135" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K135" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L135" s="7" t="inlineStr">
@@ -9091,7 +9532,7 @@
       </c>
       <c r="M135" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -9142,9 +9583,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K136" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K136" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L136" s="7" t="inlineStr">
@@ -9154,7 +9595,7 @@
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -9205,9 +9646,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K137" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K137" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L137" s="7" t="inlineStr">
@@ -9217,7 +9658,7 @@
       </c>
       <c r="M137" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -9268,9 +9709,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K138" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K138" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L138" s="7" t="inlineStr">
@@ -9280,7 +9721,7 @@
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -9331,9 +9772,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K139" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K139" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L139" s="7" t="inlineStr">
@@ -9343,7 +9784,7 @@
       </c>
       <c r="M139" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -9394,9 +9835,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K140" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K140" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L140" s="7" t="inlineStr">
@@ -9406,7 +9847,7 @@
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -9457,9 +9898,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K141" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K141" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L141" s="7" t="inlineStr">
@@ -9469,7 +9910,7 @@
       </c>
       <c r="M141" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -9520,9 +9961,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K142" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K142" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L142" s="7" t="inlineStr">
@@ -9532,7 +9973,7 @@
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -9583,9 +10024,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K143" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K143" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L143" s="7" t="inlineStr">
@@ -9595,7 +10036,7 @@
       </c>
       <c r="M143" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -9646,9 +10087,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K144" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K144" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L144" s="7" t="inlineStr">
@@ -9658,7 +10099,7 @@
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -9709,9 +10150,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K145" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K145" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L145" s="7" t="inlineStr">
@@ -9721,7 +10162,7 @@
       </c>
       <c r="M145" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -9772,9 +10213,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K146" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K146" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L146" s="7" t="inlineStr">
@@ -9784,7 +10225,7 @@
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -9835,9 +10276,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K147" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K147" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L147" s="7" t="inlineStr">
@@ -9847,7 +10288,7 @@
       </c>
       <c r="M147" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -9898,9 +10339,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K148" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K148" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L148" s="7" t="inlineStr">
@@ -9910,7 +10351,7 @@
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -9961,9 +10402,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K149" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K149" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L149" s="7" t="inlineStr">
@@ -9973,7 +10414,7 @@
       </c>
       <c r="M149" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -10024,9 +10465,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K150" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K150" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L150" s="7" t="inlineStr">
@@ -10036,7 +10477,7 @@
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -10087,9 +10528,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K151" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K151" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L151" s="7" t="inlineStr">
@@ -10099,7 +10540,7 @@
       </c>
       <c r="M151" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -10150,9 +10591,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K152" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K152" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L152" s="7" t="inlineStr">
@@ -10162,7 +10603,7 @@
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -10213,9 +10654,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K153" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K153" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L153" s="7" t="inlineStr">
@@ -10225,7 +10666,7 @@
       </c>
       <c r="M153" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -10276,9 +10717,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K154" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L154" s="7" t="inlineStr">
@@ -10288,7 +10729,7 @@
       </c>
       <c r="M154" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -10339,9 +10780,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K155" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K155" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L155" s="7" t="inlineStr">
@@ -10351,7 +10792,7 @@
       </c>
       <c r="M155" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -10402,9 +10843,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K156" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K156" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L156" s="7" t="inlineStr">
@@ -10414,7 +10855,7 @@
       </c>
       <c r="M156" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -10465,9 +10906,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K157" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K157" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L157" s="7" t="inlineStr">
@@ -10477,7 +10918,7 @@
       </c>
       <c r="M157" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -10528,9 +10969,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K158" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K158" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L158" s="7" t="inlineStr">
@@ -10540,7 +10981,7 @@
       </c>
       <c r="M158" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -10591,9 +11032,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K159" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K159" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L159" s="7" t="inlineStr">
@@ -10603,7 +11044,7 @@
       </c>
       <c r="M159" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -10654,9 +11095,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K160" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K160" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L160" s="7" t="inlineStr">
@@ -10666,7 +11107,7 @@
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -10717,9 +11158,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K161" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K161" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L161" s="7" t="inlineStr">
@@ -10729,7 +11170,7 @@
       </c>
       <c r="M161" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -10780,9 +11221,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K162" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K162" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L162" s="7" t="inlineStr">
@@ -10792,7 +11233,7 @@
       </c>
       <c r="M162" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -10843,9 +11284,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K163" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K163" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L163" s="7" t="inlineStr">
@@ -10855,7 +11296,7 @@
       </c>
       <c r="M163" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -10906,9 +11347,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K164" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K164" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L164" s="7" t="inlineStr">
@@ -10918,7 +11359,7 @@
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -10969,9 +11410,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K165" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K165" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L165" s="7" t="inlineStr">
@@ -10981,7 +11422,7 @@
       </c>
       <c r="M165" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -11032,9 +11473,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K166" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K166" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L166" s="7" t="inlineStr">
@@ -11044,7 +11485,7 @@
       </c>
       <c r="M166" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -11095,9 +11536,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K167" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K167" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L167" s="7" t="inlineStr">
@@ -11107,7 +11548,7 @@
       </c>
       <c r="M167" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -11158,9 +11599,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K168" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K168" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L168" s="7" t="inlineStr">
@@ -11170,7 +11611,7 @@
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -11221,9 +11662,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K169" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K169" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L169" s="7" t="inlineStr">
@@ -11233,7 +11674,7 @@
       </c>
       <c r="M169" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -11284,9 +11725,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K170" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K170" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L170" s="7" t="inlineStr">
@@ -11296,7 +11737,7 @@
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -11347,9 +11788,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K171" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K171" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L171" s="7" t="inlineStr">
@@ -11359,7 +11800,7 @@
       </c>
       <c r="M171" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -11410,9 +11851,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K172" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K172" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L172" s="7" t="inlineStr">
@@ -11422,7 +11863,7 @@
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -11473,9 +11914,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K173" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K173" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L173" s="7" t="inlineStr">
@@ -11485,7 +11926,7 @@
       </c>
       <c r="M173" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -11536,9 +11977,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K174" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K174" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L174" s="7" t="inlineStr">
@@ -11548,7 +11989,7 @@
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -11599,9 +12040,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K175" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K175" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L175" s="7" t="inlineStr">
@@ -11611,7 +12052,7 @@
       </c>
       <c r="M175" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -11662,9 +12103,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K176" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K176" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L176" s="7" t="inlineStr">
@@ -11674,7 +12115,7 @@
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -11725,9 +12166,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K177" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K177" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L177" s="7" t="inlineStr">
@@ -11737,7 +12178,7 @@
       </c>
       <c r="M177" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -11788,9 +12229,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K178" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K178" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L178" s="7" t="inlineStr">
@@ -11800,7 +12241,7 @@
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -11851,9 +12292,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K179" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K179" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L179" s="7" t="inlineStr">
@@ -11863,7 +12304,7 @@
       </c>
       <c r="M179" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -11914,9 +12355,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K180" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K180" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L180" s="7" t="inlineStr">
@@ -11926,7 +12367,7 @@
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -11977,9 +12418,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K181" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K181" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L181" s="7" t="inlineStr">
@@ -11989,7 +12430,7 @@
       </c>
       <c r="M181" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -12040,9 +12481,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K182" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K182" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L182" s="7" t="inlineStr">
@@ -12052,7 +12493,7 @@
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -12103,9 +12544,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K183" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K183" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L183" s="7" t="inlineStr">
@@ -12115,7 +12556,7 @@
       </c>
       <c r="M183" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -12166,9 +12607,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K184" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K184" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L184" s="7" t="inlineStr">
@@ -12178,7 +12619,7 @@
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -12229,9 +12670,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K185" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K185" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L185" s="7" t="inlineStr">
@@ -12241,7 +12682,7 @@
       </c>
       <c r="M185" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -12292,9 +12733,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K186" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K186" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L186" s="7" t="inlineStr">
@@ -12304,7 +12745,7 @@
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -12355,9 +12796,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K187" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K187" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L187" s="7" t="inlineStr">
@@ -12367,7 +12808,7 @@
       </c>
       <c r="M187" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -12418,9 +12859,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K188" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K188" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L188" s="7" t="inlineStr">
@@ -12430,7 +12871,7 @@
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -12481,9 +12922,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K189" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K189" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L189" s="7" t="inlineStr">
@@ -12493,7 +12934,7 @@
       </c>
       <c r="M189" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -12544,9 +12985,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K190" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K190" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L190" s="7" t="inlineStr">
@@ -12556,7 +12997,7 @@
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -12607,9 +13048,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K191" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K191" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L191" s="7" t="inlineStr">
@@ -12619,7 +13060,7 @@
       </c>
       <c r="M191" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -12670,9 +13111,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K192" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K192" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L192" s="7" t="inlineStr">
@@ -12682,7 +13123,7 @@
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -12733,9 +13174,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K193" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K193" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L193" s="7" t="inlineStr">
@@ -12745,7 +13186,7 @@
       </c>
       <c r="M193" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -12796,9 +13237,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K194" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K194" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L194" s="7" t="inlineStr">
@@ -12808,7 +13249,7 @@
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -12859,9 +13300,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K195" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K195" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L195" s="7" t="inlineStr">
@@ -12871,7 +13312,7 @@
       </c>
       <c r="M195" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -12922,9 +13363,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K196" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K196" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L196" s="7" t="inlineStr">
@@ -12934,7 +13375,7 @@
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -12985,9 +13426,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K197" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K197" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L197" s="7" t="inlineStr">
@@ -12997,7 +13438,7 @@
       </c>
       <c r="M197" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -13048,9 +13489,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K198" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K198" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L198" s="7" t="inlineStr">
@@ -13060,7 +13501,7 @@
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -13111,9 +13552,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K199" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K199" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L199" s="7" t="inlineStr">
@@ -13123,7 +13564,7 @@
       </c>
       <c r="M199" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -13174,9 +13615,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K200" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K200" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L200" s="7" t="inlineStr">
@@ -13186,7 +13627,7 @@
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -13237,9 +13678,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K201" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K201" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L201" s="7" t="inlineStr">
@@ -13249,7 +13690,7 @@
       </c>
       <c r="M201" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -13300,9 +13741,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K202" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K202" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L202" s="7" t="inlineStr">
@@ -13312,7 +13753,7 @@
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -13363,9 +13804,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K203" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K203" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L203" s="7" t="inlineStr">
@@ -13375,7 +13816,7 @@
       </c>
       <c r="M203" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -13426,9 +13867,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K204" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K204" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L204" s="7" t="inlineStr">
@@ -13438,7 +13879,7 @@
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -13489,9 +13930,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K205" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K205" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L205" s="7" t="inlineStr">
@@ -13501,7 +13942,7 @@
       </c>
       <c r="M205" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -13552,9 +13993,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K206" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K206" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L206" s="7" t="inlineStr">
@@ -13564,7 +14005,7 @@
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -13615,9 +14056,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K207" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K207" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L207" s="7" t="inlineStr">
@@ -13627,7 +14068,7 @@
       </c>
       <c r="M207" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -13678,9 +14119,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K208" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K208" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L208" s="7" t="inlineStr">
@@ -13690,7 +14131,7 @@
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -13741,9 +14182,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K209" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K209" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L209" s="7" t="inlineStr">
@@ -13753,7 +14194,7 @@
       </c>
       <c r="M209" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -13804,9 +14245,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K210" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K210" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L210" s="7" t="inlineStr">
@@ -13816,7 +14257,7 @@
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -13867,9 +14308,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K211" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K211" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L211" s="7" t="inlineStr">
@@ -13879,7 +14320,7 @@
       </c>
       <c r="M211" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -13930,9 +14371,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K212" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K212" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L212" s="7" t="inlineStr">
@@ -13942,7 +14383,7 @@
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -13993,9 +14434,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K213" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K213" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L213" s="7" t="inlineStr">
@@ -14005,7 +14446,7 @@
       </c>
       <c r="M213" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -14056,9 +14497,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K214" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K214" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L214" s="7" t="inlineStr">
@@ -14068,7 +14509,7 @@
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -14119,9 +14560,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K215" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K215" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L215" s="7" t="inlineStr">
@@ -14131,7 +14572,7 @@
       </c>
       <c r="M215" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -14182,9 +14623,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K216" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K216" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L216" s="7" t="inlineStr">
@@ -14194,7 +14635,7 @@
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -14245,9 +14686,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K217" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K217" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L217" s="7" t="inlineStr">
@@ -14257,7 +14698,7 @@
       </c>
       <c r="M217" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -14308,9 +14749,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K218" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K218" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L218" s="7" t="inlineStr">
@@ -14320,7 +14761,7 @@
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -14371,9 +14812,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K219" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K219" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L219" s="7" t="inlineStr">
@@ -14383,7 +14824,7 @@
       </c>
       <c r="M219" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -14434,9 +14875,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K220" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K220" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L220" s="7" t="inlineStr">
@@ -14446,7 +14887,7 @@
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -14497,9 +14938,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K221" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K221" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L221" s="7" t="inlineStr">
@@ -14509,7 +14950,7 @@
       </c>
       <c r="M221" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -14560,9 +15001,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K222" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K222" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L222" s="7" t="inlineStr">
@@ -14572,7 +15013,7 @@
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -14623,9 +15064,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K223" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K223" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L223" s="7" t="inlineStr">
@@ -14635,7 +15076,7 @@
       </c>
       <c r="M223" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -14686,9 +15127,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K224" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K224" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L224" s="7" t="inlineStr">
@@ -14698,7 +15139,7 @@
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -14749,9 +15190,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K225" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K225" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L225" s="7" t="inlineStr">
@@ -14761,7 +15202,7 @@
       </c>
       <c r="M225" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -14812,9 +15253,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K226" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K226" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L226" s="7" t="inlineStr">
@@ -14824,7 +15265,7 @@
       </c>
       <c r="M226" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -14875,9 +15316,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K227" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K227" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L227" s="7" t="inlineStr">
@@ -14887,7 +15328,7 @@
       </c>
       <c r="M227" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -14938,9 +15379,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K228" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K228" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L228" s="7" t="inlineStr">
@@ -14950,7 +15391,7 @@
       </c>
       <c r="M228" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -15001,9 +15442,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K229" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K229" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L229" s="7" t="inlineStr">
@@ -15013,7 +15454,7 @@
       </c>
       <c r="M229" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -15064,9 +15505,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K230" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K230" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L230" s="7" t="inlineStr">
@@ -15076,7 +15517,7 @@
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -15127,9 +15568,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K231" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K231" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L231" s="7" t="inlineStr">
@@ -15139,7 +15580,7 @@
       </c>
       <c r="M231" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -15190,9 +15631,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K232" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K232" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L232" s="7" t="inlineStr">
@@ -15202,7 +15643,7 @@
       </c>
       <c r="M232" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -15253,9 +15694,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K233" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K233" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L233" s="7" t="inlineStr">
@@ -15265,7 +15706,7 @@
       </c>
       <c r="M233" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -15316,9 +15757,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K234" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K234" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L234" s="7" t="inlineStr">
@@ -15328,7 +15769,7 @@
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -15379,9 +15820,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K235" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K235" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L235" s="7" t="inlineStr">
@@ -15391,7 +15832,7 @@
       </c>
       <c r="M235" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -15442,9 +15883,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K236" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K236" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L236" s="7" t="inlineStr">
@@ -15454,7 +15895,7 @@
       </c>
       <c r="M236" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -15505,9 +15946,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K237" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K237" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L237" s="7" t="inlineStr">
@@ -15517,7 +15958,7 @@
       </c>
       <c r="M237" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -15568,9 +16009,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K238" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K238" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L238" s="7" t="inlineStr">
@@ -15580,7 +16021,7 @@
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -15631,9 +16072,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K239" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K239" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L239" s="7" t="inlineStr">
@@ -15643,7 +16084,7 @@
       </c>
       <c r="M239" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -15694,9 +16135,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K240" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K240" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L240" s="7" t="inlineStr">
@@ -15706,7 +16147,7 @@
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -15757,9 +16198,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K241" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K241" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L241" s="7" t="inlineStr">
@@ -15769,7 +16210,7 @@
       </c>
       <c r="M241" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -15820,9 +16261,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K242" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K242" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L242" s="7" t="inlineStr">
@@ -15832,7 +16273,7 @@
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -15883,9 +16324,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K243" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K243" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L243" s="7" t="inlineStr">
@@ -15895,7 +16336,7 @@
       </c>
       <c r="M243" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -15946,9 +16387,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K244" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K244" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L244" s="7" t="inlineStr">
@@ -15958,7 +16399,7 @@
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -16009,9 +16450,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K245" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K245" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L245" s="7" t="inlineStr">
@@ -16021,7 +16462,7 @@
       </c>
       <c r="M245" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -16072,9 +16513,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K246" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K246" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L246" s="7" t="inlineStr">
@@ -16084,7 +16525,7 @@
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -16135,9 +16576,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K247" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K247" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L247" s="7" t="inlineStr">
@@ -16147,7 +16588,7 @@
       </c>
       <c r="M247" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -16198,9 +16639,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K248" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K248" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L248" s="7" t="inlineStr">
@@ -16210,7 +16651,7 @@
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -16261,9 +16702,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K249" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K249" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L249" s="7" t="inlineStr">
@@ -16273,7 +16714,7 @@
       </c>
       <c r="M249" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -16324,9 +16765,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K250" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K250" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L250" s="7" t="inlineStr">
@@ -16336,7 +16777,7 @@
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -16387,9 +16828,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K251" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K251" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L251" s="7" t="inlineStr">
@@ -16399,7 +16840,7 @@
       </c>
       <c r="M251" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -16450,9 +16891,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K252" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K252" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L252" s="7" t="inlineStr">
@@ -16462,7 +16903,7 @@
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -16513,9 +16954,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K253" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K253" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L253" s="7" t="inlineStr">
@@ -16525,7 +16966,7 @@
       </c>
       <c r="M253" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -16576,9 +17017,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K254" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K254" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L254" s="7" t="inlineStr">
@@ -16588,7 +17029,7 @@
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -16639,9 +17080,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K255" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K255" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L255" s="7" t="inlineStr">
@@ -16651,7 +17092,7 @@
       </c>
       <c r="M255" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -16702,9 +17143,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K256" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K256" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L256" s="7" t="inlineStr">
@@ -16714,7 +17155,7 @@
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -16765,9 +17206,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K257" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K257" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L257" s="7" t="inlineStr">
@@ -16777,7 +17218,7 @@
       </c>
       <c r="M257" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -16828,9 +17269,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K258" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K258" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L258" s="7" t="inlineStr">
@@ -16840,7 +17281,7 @@
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -16891,9 +17332,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K259" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K259" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L259" s="7" t="inlineStr">
@@ -16903,7 +17344,7 @@
       </c>
       <c r="M259" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -16954,9 +17395,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K260" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K260" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L260" s="7" t="inlineStr">
@@ -16966,7 +17407,7 @@
       </c>
       <c r="M260" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -17017,9 +17458,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K261" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K261" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L261" s="7" t="inlineStr">
@@ -17029,7 +17470,7 @@
       </c>
       <c r="M261" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -17080,9 +17521,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K262" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K262" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L262" s="7" t="inlineStr">
@@ -17092,7 +17533,7 @@
       </c>
       <c r="M262" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -17143,9 +17584,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K263" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K263" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L263" s="7" t="inlineStr">
@@ -17155,7 +17596,7 @@
       </c>
       <c r="M263" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -17206,9 +17647,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K264" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K264" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L264" s="7" t="inlineStr">
@@ -17218,7 +17659,7 @@
       </c>
       <c r="M264" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -17269,9 +17710,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K265" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K265" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L265" s="7" t="inlineStr">
@@ -17281,7 +17722,7 @@
       </c>
       <c r="M265" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -17332,9 +17773,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K266" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K266" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L266" s="7" t="inlineStr">
@@ -17344,7 +17785,7 @@
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -17395,9 +17836,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K267" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K267" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L267" s="7" t="inlineStr">
@@ -17407,7 +17848,7 @@
       </c>
       <c r="M267" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -17458,9 +17899,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K268" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K268" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L268" s="7" t="inlineStr">
@@ -17470,7 +17911,7 @@
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -17521,9 +17962,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K269" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K269" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L269" s="7" t="inlineStr">
@@ -17533,7 +17974,7 @@
       </c>
       <c r="M269" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -17584,9 +18025,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K270" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K270" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L270" s="7" t="inlineStr">
@@ -17596,7 +18037,7 @@
       </c>
       <c r="M270" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -17647,9 +18088,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K271" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K271" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L271" s="7" t="inlineStr">
@@ -17659,7 +18100,7 @@
       </c>
       <c r="M271" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -17710,9 +18151,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K272" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K272" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L272" s="7" t="inlineStr">
@@ -17722,7 +18163,7 @@
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -17773,9 +18214,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K273" s="5" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K273" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L273" s="7" t="inlineStr">
@@ -17785,7 +18226,7 @@
       </c>
       <c r="M273" s="6" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -17836,9 +18277,9 @@
           <t>Upstream</t>
         </is>
       </c>
-      <c r="K274" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K274" s="16" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="L274" s="7" t="inlineStr">
@@ -17848,7 +18289,7 @@
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
-          <t>Spurious NOW_ASSIST_ENABLED guard on plain Table API tool — remove guard</t>
+          <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
     </row>
@@ -17858,410 +18299,337 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="72" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Tool returned real ServiceNow data with expected shape</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>Tool errored, threw, or returned HTTP error</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Fishy</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Tool returned 200 but suspicious output (wrong data, silent state mismatch)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>Pre-condition not met — plugin missing, flag off, guard blocked call</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Root Cause Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Wrong table name</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Implementation references a non-existent ServiceNow table</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>Workflow gate</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>ServiceNow Business Rule blocks direct Table API state transition</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Broken round-trip</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>Tool A creates a record, Tool B cannot operate on it using the returned ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>Silent lie</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>Tool returns HTTP 200 success but the intended change did not happen</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>PDI config</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>Requires PDI setup not present on a standard free PDI</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Misleading name</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>Tool name implies broader capability than the implementation delivers</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Now Assist guard — genuine</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>Tool legitimately requires Now Assist plugin (nlq_query, ai_search, etc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>Now Assist guard — spurious</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>Plain Table API tool incorrectly blocked because requireNowAssist() is called at the top of executeNowAssistToolCall() before the switch, blocking all tools dispatched to that handler</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Fix Complexity</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>Table name fix or guard removal — straightforward code change, verifiable in minutes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>Needs investigation before fixing (source dive, PDI verification, or API research required)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>Touches workflow engine, plugin dependency, or requires non-trivial ServiceNow API research</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Upstream or Fork Fix</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Fork</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>Fix stays in Solvvision fork only — not suitable for upstream PR</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>Upstream</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>Worth raising as PR or issue to aartiq/servicenow-mcp — affects all users</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>Not yet actioned</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>Fix being actively worked on</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>Fix committed to fork</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>Wont Fix</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>Accepted as-is and documented</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>Phase Discovered</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>Found during 30-prompt manual checklist run (2026-05-04)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>Found during automated full-coverage harness run (2026-05-04)</t>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>Issue #</t>
+        </is>
+      </c>
+      <c r="B1" s="17" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="C1" s="17" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="D1" s="17" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" s="17" t="inlineStr">
+        <is>
+          <t>Why Deferred</t>
+        </is>
+      </c>
+      <c r="F1" s="17" t="inlineStr">
+        <is>
+          <t>Target Wave / Release</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr"/>
+      <c r="B2" s="18" t="inlineStr">
+        <is>
+          <t>nlq_query</t>
+        </is>
+      </c>
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t>now-assist</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="inlineStr">
+        <is>
+          <t>Ask a natural language question and get structured ServiceNow data (ServiceNow NLQ API)</t>
+        </is>
+      </c>
+      <c r="E2" s="18" t="inlineStr">
+        <is>
+          <t>Requires Now Assist plugin — not enabled in Solvvision v1 deployment</t>
+        </is>
+      </c>
+      <c r="F2" s="18" t="inlineStr">
+        <is>
+          <t>v2 — post Now Assist enablement</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr"/>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>ai_search</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>now-assist</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>Semantic AI-powered search across KB, catalog, incidents (ServiceNow AI Search)</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>Requires Now Assist plugin — not enabled in Solvvision v1 deployment</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>v2 — post Now Assist enablement</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr"/>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>generate_summary</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>now-assist</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>Generate an AI summary of any record using Now Assist (latest release: sn_assist/skill/summarize)</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>Requires Now Assist plugin — not enabled in Solvvision v1 deployment</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>v2 — post Now Assist enablement</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr"/>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>suggest_resolution</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>now-assist</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Get AI-powered resolution suggestion for an incident based on similar past incidents</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>Requires Now Assist plugin — not enabled in Solvvision v1 deployment</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>v2 — post Now Assist enablement</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr"/>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>categorize_incident</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>now-assist</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>Use Predictive Intelligence to predict category, assignment group, and priority (latest release: LightGBM algorithm)</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>Requires Now Assist plugin — not enabled in Solvvision v1 deployment</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>v2 — post Now Assist enablement</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr"/>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>get_virtual_agent_topics</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>now-assist</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>List Virtual Agent topics available in the instance (latest release: streaming VA API)</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>Requires Now Assist plugin — not enabled in Solvvision v1 deployment</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>v2 — post Now Assist enablement</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr"/>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>trigger_agentic_playbook</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>now-assist</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>Invoke an Agentic Playbook — context-aware AI agents that complete tasks autonomously</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>Requires Now Assist plugin — not enabled in Solvvision v1 deployment</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>v2 — post Now Assist enablement</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr"/>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>get_ms_copilot_topics</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>now-assist</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>List VA topics exposed to Microsoft Copilot 365 via Custom Engine Agent integration</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>Requires Now Assist plugin — not enabled in Solvvision v1 deployment</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>v2 — post Now Assist enablement</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr"/>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>generate_work_notes</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>now-assist</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Generate AI-drafted work notes for a record based on its current context</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>Requires Now Assist plugin — not enabled in Solvvision v1 deployment</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>v2 — post Now Assist enablement</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr"/>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>get_pi_models</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>now-assist</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>List available Predictive Intelligence solutions (classification/similarity models)</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>Requires Now Assist plugin — not enabled in Solvvision v1 deployment</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>v2 — post Now Assist enablement</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/solvvision/solvvision-mcp-findings.xlsx
+++ b/solvvision/solvvision-mcp-findings.xlsx
@@ -991,7 +991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M274"/>
+  <dimension ref="A1:M287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -18290,6 +18290,851 @@
       <c r="M274" s="3" t="inlineStr">
         <is>
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>13</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>trigger_flow / test_flow — Invalid table sys_hub_flow_trigger does not exist</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>flow</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>trigger_flow, test_flow</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Wrong table name</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Flows must be triggered via REST API endpoint (POST /api/now/flow_api/...) not via Table API insert into sys_hub_flow_trigger. Rewrite handler to use the Flow Designer REST API.</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>Fork</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>sys_hub_flow_trigger is not a writable ServiceNow table. Flow triggering requires the Flow Designer API.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>14</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>list_subflows / get_subflow / create_subflow — Invalid table sys_hub_subflow does not exist</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>flow</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>list_subflows, get_subflow, create_subflow</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Wrong table name</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Subflows are stored in sys_hub_flow with type=subflow. Change all three handlers to query sys_hub_flow with ^type=subflow appended to the encoded query.</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>Fork</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>sys_hub_subflow is not a ServiceNow table. Both list and get must filter sys_hub_flow by type=subflow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>15</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>list_portal_pages — sp_portal filter silently ignored; returns all pages</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>list_portal_pages</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Fishy</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Wrong filter field</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Verify that the encoded query uses sp_portal=&lt;sys_id&gt; (the reference field on sp_page). If the handler uses portal= or portal_id=, correct to sp_portal=.</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Fork</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>50 records returned when filtering by newly-created portal; expected 0. Filter field name mismatch suspected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>16</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>list_ux_pages — ux_app_config filter silently ignored; returns all pages</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>list_ux_pages</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Fishy</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Wrong filter field</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Verify the encoded query field for UX app filtering on sys_ux_page. The field may be sys_scope or application, not ux_app_config.</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>Fork</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>22 records returned when filtering by fake app_sys_id; expected 0. Filter field likely wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>17</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>get_event_registry_entry — filter uses wrong field name; returns first record regardless of query</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>integration</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>get_event_registry_entry</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Fishy</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Wrong filter field</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Change encoded query from name=&lt;value&gt; to event_name=&lt;value&gt; on sysevent_register table.</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>Fork</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>sysevent_register uses event_name as the primary identifier, not name. Query with name= silently ignores filter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>18</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>register_event — event_name field empty on created record; sets 'name' instead of 'event_name'</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>integration</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>register_event</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Fishy</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Wrong field name</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>In createRecord payload, change key 'name' to 'event_name' to match the sysevent_register schema.</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>Fork</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>Record sys_id 0cafcb3b83e40310ad3cc4d0deaad3c9 created with empty event_name. Cleanup required on PDI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>19</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>list_homepages — Invalid table sys_ui_hp does not exist</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>performance</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>list_homepages</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Wrong table name</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Correct table for homepages is sys_ui_homepage. Update the queryRecords call accordingly.</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>Fork</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>sys_ui_hp is not a ServiceNow table. Standard homepages are in sys_ui_homepage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>20</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>list_pa_jobs / get_pa_job — Invalid table pa_job does not exist</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>performance</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>list_pa_jobs, get_pa_job</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Wrong table name</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>The correct table for PA collection jobs is sysauto_pa_job. Update both handlers.</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>Fork</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>pa_job does not exist on standard ServiceNow instances. Confirmed INVALID_REQUEST on PDI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>21</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>export_properties — category filter silently ignored; returns all 500 properties</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>sys-properties</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>export_properties</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Fishy</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Wrong filter field</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Verify the sys_properties field for category. It may be category (reference) requiring a sys_id rather than the category name string. Test with actual category sys_id or use sys_properties_category join.</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>Fork</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>PDI may have uncategorised properties only, making this hard to isolate. Verify on production-like instance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>22</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>get_va_conversation — Invalid table sys_cs_conversation_message does not exist</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>va</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>get_va_conversation</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Wrong table name</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>VA conversation messages are in sys_cs_chat_queue_message or similar. Investigate correct table via sys_db_object query on a licensed instance.</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>Fork</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>sys_cs_conversation_message is not a standard table. Correct table may require Conversational Platform license.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>23</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>list_va_categories — Invalid table sys_cs_category does not exist</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>va</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>list_va_categories</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Wrong table name</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>VA categories use sys_cs_category_config or are embedded in topic records. Verify correct table on a licensed NLU instance.</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>Fork</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>sys_cs_category is not a standard ServiceNow table. Category data may be stored differently in newer VA versions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>24</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>get_performance_analytics — fallback hits invalid table pa_job_log</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>reporting</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>get_performance_analytics</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Wrong table name</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Remove the pa_job_log fallback entirely. If the PA widget API call fails, return an error rather than querying a non-existent table.</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>Fork</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>Tool tries /api/now/pa/widget/ first; on error falls back to pa_job_log which does not exist. pa_job_log is not a standard table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>25</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>ml_model_training_history — Invalid table ml_solution_version does not exist</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>ml_model_training_history</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Wrong table name</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Correct table for PI model versions/training history is ml_solution (query training-related fields) or ml_train_result. Verify on a PI-licensed instance.</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>Fork</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>ml_solution_version is not a standard ServiceNow table. Training history may be in ml_solution or a plugin-specific table.</t>
         </is>
       </c>
     </row>

--- a/solvvision/solvvision-mcp-findings.xlsx
+++ b/solvvision/solvvision-mcp-findings.xlsx
@@ -9,11 +9,12 @@
   <sheets>
     <sheet name="Legend" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Findings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Future Features" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Waves" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Future Features" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Findings'!$A$1:$M$274</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Future Features'!$A$1:$F$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Future Features'!$A$1:$F$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -56,7 +57,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -121,6 +122,11 @@
         <bgColor rgb="00DDEEFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -162,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -216,6 +222,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -991,7 +1006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M287"/>
+  <dimension ref="A1:O287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1007,6 +1022,8 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1075,6 +1092,16 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="N1" s="19" t="inlineStr">
+        <is>
+          <t>Wave Discovered</t>
+        </is>
+      </c>
+      <c r="O1" s="19" t="inlineStr">
+        <is>
+          <t>Wave Fixed</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="72" customHeight="1">
       <c r="A2" s="2" t="n">
@@ -1140,6 +1167,12 @@
           <t>Surfaced in Phase 1 #2. Returned 3 articles unrelated to query 'email'. Likely body-text-only match or keyword silently dropped.</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3" ht="72" customHeight="1">
       <c r="A3" s="5" t="n">
@@ -1205,6 +1238,12 @@
           <t>state=2 via update_incident works fine. Business Rule gates state=6 (Resolved) and state=7 (Closed). Both tools affected by same pattern.</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4" ht="72" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -1270,6 +1309,12 @@
           <t>member_sys_id f3e4b59f...3fd returned by add_user_to_group. deleteRecord with that sys_id returns NOT_FOUND. Compound key mismatch suspected.</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5" ht="72" customHeight="1">
       <c r="A5" s="5" t="n">
@@ -1335,6 +1380,12 @@
           <t>sysapproval_rule is not a standard ServiceNow table. Approval rules are typically in sysrule_approvals.</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6" ht="72" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -1400,6 +1451,12 @@
           <t>list_atf_tests and get_atf_test both pass with correct tables. Only results/insight reads are broken.</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7" ht="72" customHeight="1">
       <c r="A7" s="5" t="n">
@@ -1465,6 +1522,16 @@
           <t>sys_report_schedule is not a standard ServiceNow table. Scheduled reports likely live in sysauto_report.</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="72" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -1530,6 +1597,12 @@
           <t>sysauto_trigger_log is not a standard ServiceNow table. Correct table likely sysauto_trigger (no _log suffix).</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9" ht="72" customHeight="1">
       <c r="A9" s="5" t="n">
@@ -1595,6 +1668,12 @@
           <t>fix_notes and cause_notes set correctly. problem_state stays at 101 after call. Response hardcodes action='resolved' regardless of actual state.</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10" ht="72" customHeight="1">
       <c r="A10" s="2" t="n">
@@ -1660,6 +1739,12 @@
           <t>Business Rule silently drops direct workflow_state PATCH. Server returns 200 but state stays 'draft'. Requires sn_km_api plugin on target instance.</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="5" t="inlineStr"/>
@@ -1723,6 +1808,12 @@
           <t>Now Assist dependency by design — remove from v1 or mark unsupported</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="inlineStr"/>
@@ -1786,6 +1877,12 @@
           <t>Now Assist dependency by design — remove from v1 or mark unsupported</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="5" t="inlineStr"/>
@@ -1849,6 +1946,12 @@
           <t>Now Assist dependency by design — remove from v1 or mark unsupported</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="2" t="inlineStr"/>
@@ -1912,6 +2015,12 @@
           <t>Now Assist dependency by design — remove from v1 or mark unsupported</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="5" t="inlineStr"/>
@@ -1975,6 +2084,12 @@
           <t>Now Assist dependency by design — remove from v1 or mark unsupported</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="inlineStr"/>
@@ -2038,6 +2153,12 @@
           <t>Now Assist dependency by design — remove from v1 or mark unsupported</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="5" t="inlineStr"/>
@@ -2101,6 +2222,12 @@
           <t>Now Assist dependency by design — remove from v1 or mark unsupported</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18" ht="60" customHeight="1">
       <c r="A18" s="2" t="inlineStr"/>
@@ -2164,6 +2291,12 @@
           <t>Now Assist dependency by design — remove from v1 or mark unsupported</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="5" t="inlineStr"/>
@@ -2227,6 +2360,12 @@
           <t>Now Assist dependency by design — remove from v1 or mark unsupported</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="2" t="inlineStr"/>
@@ -2290,6 +2429,12 @@
           <t>Now Assist dependency by design — remove from v1 or mark unsupported</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="5" t="inlineStr"/>
@@ -2353,6 +2498,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="60" customHeight="1">
       <c r="A22" s="2" t="inlineStr"/>
@@ -2416,6 +2571,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="60" customHeight="1">
       <c r="A23" s="5" t="inlineStr"/>
@@ -2479,6 +2644,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="60" customHeight="1">
       <c r="A24" s="2" t="inlineStr"/>
@@ -2542,6 +2717,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="60" customHeight="1">
       <c r="A25" s="5" t="inlineStr"/>
@@ -2605,6 +2790,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="60" customHeight="1">
       <c r="A26" s="2" t="inlineStr"/>
@@ -2668,6 +2863,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="60" customHeight="1">
       <c r="A27" s="5" t="inlineStr"/>
@@ -2731,6 +2936,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="60" customHeight="1">
       <c r="A28" s="2" t="inlineStr"/>
@@ -2794,6 +3009,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="60" customHeight="1">
       <c r="A29" s="5" t="inlineStr"/>
@@ -2857,6 +3082,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="60" customHeight="1">
       <c r="A30" s="2" t="inlineStr"/>
@@ -2920,6 +3155,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="60" customHeight="1">
       <c r="A31" s="5" t="inlineStr"/>
@@ -2983,6 +3228,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="60" customHeight="1">
       <c r="A32" s="2" t="inlineStr"/>
@@ -3046,6 +3301,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="60" customHeight="1">
       <c r="A33" s="5" t="inlineStr"/>
@@ -3109,6 +3374,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="60" customHeight="1">
       <c r="A34" s="2" t="inlineStr"/>
@@ -3172,6 +3447,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="60" customHeight="1">
       <c r="A35" s="5" t="inlineStr"/>
@@ -3235,6 +3520,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="60" customHeight="1">
       <c r="A36" s="2" t="inlineStr"/>
@@ -3298,6 +3593,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="60" customHeight="1">
       <c r="A37" s="5" t="inlineStr"/>
@@ -3361,6 +3666,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="60" customHeight="1">
       <c r="A38" s="2" t="inlineStr"/>
@@ -3424,6 +3739,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="60" customHeight="1">
       <c r="A39" s="5" t="inlineStr"/>
@@ -3487,6 +3812,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="60" customHeight="1">
       <c r="A40" s="2" t="inlineStr"/>
@@ -3550,6 +3885,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="60" customHeight="1">
       <c r="A41" s="5" t="inlineStr"/>
@@ -3613,6 +3958,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="60" customHeight="1">
       <c r="A42" s="2" t="inlineStr"/>
@@ -3676,6 +4031,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="60" customHeight="1">
       <c r="A43" s="5" t="inlineStr"/>
@@ -3739,6 +4104,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="60" customHeight="1">
       <c r="A44" s="2" t="inlineStr"/>
@@ -3802,6 +4177,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="60" customHeight="1">
       <c r="A45" s="5" t="inlineStr"/>
@@ -3865,6 +4250,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="60" customHeight="1">
       <c r="A46" s="2" t="inlineStr"/>
@@ -3928,6 +4323,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="60" customHeight="1">
       <c r="A47" s="5" t="inlineStr"/>
@@ -3991,6 +4396,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="60" customHeight="1">
       <c r="A48" s="2" t="inlineStr"/>
@@ -4054,6 +4469,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="60" customHeight="1">
       <c r="A49" s="5" t="inlineStr"/>
@@ -4117,6 +4542,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="60" customHeight="1">
       <c r="A50" s="2" t="inlineStr"/>
@@ -4180,6 +4615,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="60" customHeight="1">
       <c r="A51" s="5" t="inlineStr"/>
@@ -4243,6 +4688,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="60" customHeight="1">
       <c r="A52" s="2" t="inlineStr"/>
@@ -4306,6 +4761,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="60" customHeight="1">
       <c r="A53" s="5" t="inlineStr"/>
@@ -4369,6 +4834,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="60" customHeight="1">
       <c r="A54" s="2" t="inlineStr"/>
@@ -4432,6 +4907,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="60" customHeight="1">
       <c r="A55" s="5" t="inlineStr"/>
@@ -4495,6 +4980,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="60" customHeight="1">
       <c r="A56" s="2" t="inlineStr"/>
@@ -4558,6 +5053,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="60" customHeight="1">
       <c r="A57" s="5" t="inlineStr"/>
@@ -4621,6 +5126,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="60" customHeight="1">
       <c r="A58" s="2" t="inlineStr"/>
@@ -4684,6 +5199,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="60" customHeight="1">
       <c r="A59" s="5" t="inlineStr"/>
@@ -4747,6 +5272,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="60" customHeight="1">
       <c r="A60" s="2" t="inlineStr"/>
@@ -4810,6 +5345,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="60" customHeight="1">
       <c r="A61" s="5" t="inlineStr"/>
@@ -4873,6 +5418,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="60" customHeight="1">
       <c r="A62" s="2" t="inlineStr"/>
@@ -4936,6 +5491,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="60" customHeight="1">
       <c r="A63" s="5" t="inlineStr"/>
@@ -4999,6 +5564,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="60" customHeight="1">
       <c r="A64" s="2" t="inlineStr"/>
@@ -5062,6 +5637,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="60" customHeight="1">
       <c r="A65" s="5" t="inlineStr"/>
@@ -5125,6 +5710,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="60" customHeight="1">
       <c r="A66" s="2" t="inlineStr"/>
@@ -5188,6 +5783,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="60" customHeight="1">
       <c r="A67" s="5" t="inlineStr"/>
@@ -5251,6 +5856,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="60" customHeight="1">
       <c r="A68" s="2" t="inlineStr"/>
@@ -5314,6 +5929,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="60" customHeight="1">
       <c r="A69" s="5" t="inlineStr"/>
@@ -5377,6 +6002,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="60" customHeight="1">
       <c r="A70" s="2" t="inlineStr"/>
@@ -5440,6 +6075,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="60" customHeight="1">
       <c r="A71" s="5" t="inlineStr"/>
@@ -5503,6 +6148,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="60" customHeight="1">
       <c r="A72" s="2" t="inlineStr"/>
@@ -5566,6 +6221,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="60" customHeight="1">
       <c r="A73" s="5" t="inlineStr"/>
@@ -5629,6 +6294,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="60" customHeight="1">
       <c r="A74" s="2" t="inlineStr"/>
@@ -5692,6 +6367,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="60" customHeight="1">
       <c r="A75" s="5" t="inlineStr"/>
@@ -5755,6 +6440,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="60" customHeight="1">
       <c r="A76" s="2" t="inlineStr"/>
@@ -5818,6 +6513,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="60" customHeight="1">
       <c r="A77" s="5" t="inlineStr"/>
@@ -5881,6 +6586,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="60" customHeight="1">
       <c r="A78" s="2" t="inlineStr"/>
@@ -5944,6 +6659,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="60" customHeight="1">
       <c r="A79" s="5" t="inlineStr"/>
@@ -6007,6 +6732,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="60" customHeight="1">
       <c r="A80" s="2" t="inlineStr"/>
@@ -6070,6 +6805,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="60" customHeight="1">
       <c r="A81" s="5" t="inlineStr"/>
@@ -6133,6 +6878,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="60" customHeight="1">
       <c r="A82" s="2" t="inlineStr"/>
@@ -6196,6 +6951,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="60" customHeight="1">
       <c r="A83" s="5" t="inlineStr"/>
@@ -6259,6 +7024,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="60" customHeight="1">
       <c r="A84" s="2" t="inlineStr"/>
@@ -6322,6 +7097,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="60" customHeight="1">
       <c r="A85" s="5" t="inlineStr"/>
@@ -6385,6 +7170,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="60" customHeight="1">
       <c r="A86" s="2" t="inlineStr"/>
@@ -6448,6 +7243,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="60" customHeight="1">
       <c r="A87" s="5" t="inlineStr"/>
@@ -6511,6 +7316,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="60" customHeight="1">
       <c r="A88" s="2" t="inlineStr"/>
@@ -6574,6 +7389,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="60" customHeight="1">
       <c r="A89" s="5" t="inlineStr"/>
@@ -6637,6 +7462,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="60" customHeight="1">
       <c r="A90" s="2" t="inlineStr"/>
@@ -6700,6 +7535,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="60" customHeight="1">
       <c r="A91" s="5" t="inlineStr"/>
@@ -6763,6 +7608,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="60" customHeight="1">
       <c r="A92" s="2" t="inlineStr"/>
@@ -6826,6 +7681,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="60" customHeight="1">
       <c r="A93" s="5" t="inlineStr"/>
@@ -6889,6 +7754,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="60" customHeight="1">
       <c r="A94" s="2" t="inlineStr"/>
@@ -6952,6 +7827,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="60" customHeight="1">
       <c r="A95" s="5" t="inlineStr"/>
@@ -7015,6 +7900,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="60" customHeight="1">
       <c r="A96" s="2" t="inlineStr"/>
@@ -7078,6 +7973,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="60" customHeight="1">
       <c r="A97" s="5" t="inlineStr"/>
@@ -7141,6 +8046,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="60" customHeight="1">
       <c r="A98" s="2" t="inlineStr"/>
@@ -7204,6 +8119,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="60" customHeight="1">
       <c r="A99" s="5" t="inlineStr"/>
@@ -7267,6 +8192,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="60" customHeight="1">
       <c r="A100" s="2" t="inlineStr"/>
@@ -7330,6 +8265,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="60" customHeight="1">
       <c r="A101" s="5" t="inlineStr"/>
@@ -7393,6 +8338,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="60" customHeight="1">
       <c r="A102" s="2" t="inlineStr"/>
@@ -7456,6 +8411,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="60" customHeight="1">
       <c r="A103" s="5" t="inlineStr"/>
@@ -7519,6 +8484,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="60" customHeight="1">
       <c r="A104" s="2" t="inlineStr"/>
@@ -7582,6 +8557,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="60" customHeight="1">
       <c r="A105" s="5" t="inlineStr"/>
@@ -7645,6 +8630,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="60" customHeight="1">
       <c r="A106" s="2" t="inlineStr"/>
@@ -7708,6 +8703,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="60" customHeight="1">
       <c r="A107" s="5" t="inlineStr"/>
@@ -7771,6 +8776,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="60" customHeight="1">
       <c r="A108" s="2" t="inlineStr"/>
@@ -7834,6 +8849,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="60" customHeight="1">
       <c r="A109" s="5" t="inlineStr"/>
@@ -7897,6 +8922,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="60" customHeight="1">
       <c r="A110" s="2" t="inlineStr"/>
@@ -7960,6 +8995,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="60" customHeight="1">
       <c r="A111" s="5" t="inlineStr"/>
@@ -8023,6 +9068,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="60" customHeight="1">
       <c r="A112" s="2" t="inlineStr"/>
@@ -8086,6 +9141,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="60" customHeight="1">
       <c r="A113" s="5" t="inlineStr"/>
@@ -8149,6 +9214,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="60" customHeight="1">
       <c r="A114" s="2" t="inlineStr"/>
@@ -8212,6 +9287,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="60" customHeight="1">
       <c r="A115" s="5" t="inlineStr"/>
@@ -8275,6 +9360,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="60" customHeight="1">
       <c r="A116" s="2" t="inlineStr"/>
@@ -8338,6 +9433,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="60" customHeight="1">
       <c r="A117" s="5" t="inlineStr"/>
@@ -8401,6 +9506,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="60" customHeight="1">
       <c r="A118" s="2" t="inlineStr"/>
@@ -8464,6 +9579,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="60" customHeight="1">
       <c r="A119" s="5" t="inlineStr"/>
@@ -8527,6 +9652,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="60" customHeight="1">
       <c r="A120" s="2" t="inlineStr"/>
@@ -8590,6 +9725,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="60" customHeight="1">
       <c r="A121" s="5" t="inlineStr"/>
@@ -8653,6 +9798,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="60" customHeight="1">
       <c r="A122" s="2" t="inlineStr"/>
@@ -8716,6 +9871,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="60" customHeight="1">
       <c r="A123" s="5" t="inlineStr"/>
@@ -8779,6 +9944,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="60" customHeight="1">
       <c r="A124" s="2" t="inlineStr"/>
@@ -8842,6 +10017,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="60" customHeight="1">
       <c r="A125" s="5" t="inlineStr"/>
@@ -8905,6 +10090,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="60" customHeight="1">
       <c r="A126" s="2" t="inlineStr"/>
@@ -8968,6 +10163,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="60" customHeight="1">
       <c r="A127" s="5" t="inlineStr"/>
@@ -9031,6 +10236,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="60" customHeight="1">
       <c r="A128" s="2" t="inlineStr"/>
@@ -9094,6 +10309,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="60" customHeight="1">
       <c r="A129" s="5" t="inlineStr"/>
@@ -9157,6 +10382,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="60" customHeight="1">
       <c r="A130" s="2" t="inlineStr"/>
@@ -9220,6 +10455,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="60" customHeight="1">
       <c r="A131" s="5" t="inlineStr"/>
@@ -9283,6 +10528,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="60" customHeight="1">
       <c r="A132" s="2" t="inlineStr"/>
@@ -9346,6 +10601,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="60" customHeight="1">
       <c r="A133" s="5" t="inlineStr"/>
@@ -9409,6 +10674,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="60" customHeight="1">
       <c r="A134" s="2" t="inlineStr"/>
@@ -9472,6 +10747,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="60" customHeight="1">
       <c r="A135" s="5" t="inlineStr"/>
@@ -9535,6 +10820,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="60" customHeight="1">
       <c r="A136" s="2" t="inlineStr"/>
@@ -9598,6 +10893,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="60" customHeight="1">
       <c r="A137" s="5" t="inlineStr"/>
@@ -9661,6 +10966,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="60" customHeight="1">
       <c r="A138" s="2" t="inlineStr"/>
@@ -9724,6 +11039,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="60" customHeight="1">
       <c r="A139" s="5" t="inlineStr"/>
@@ -9787,6 +11112,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="60" customHeight="1">
       <c r="A140" s="2" t="inlineStr"/>
@@ -9850,6 +11185,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="60" customHeight="1">
       <c r="A141" s="5" t="inlineStr"/>
@@ -9913,6 +11258,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="60" customHeight="1">
       <c r="A142" s="2" t="inlineStr"/>
@@ -9976,6 +11331,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="60" customHeight="1">
       <c r="A143" s="5" t="inlineStr"/>
@@ -10039,6 +11404,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="60" customHeight="1">
       <c r="A144" s="2" t="inlineStr"/>
@@ -10102,6 +11477,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="60" customHeight="1">
       <c r="A145" s="5" t="inlineStr"/>
@@ -10165,6 +11550,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="60" customHeight="1">
       <c r="A146" s="2" t="inlineStr"/>
@@ -10228,6 +11623,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="60" customHeight="1">
       <c r="A147" s="5" t="inlineStr"/>
@@ -10291,6 +11696,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="60" customHeight="1">
       <c r="A148" s="2" t="inlineStr"/>
@@ -10354,6 +11769,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="60" customHeight="1">
       <c r="A149" s="5" t="inlineStr"/>
@@ -10417,6 +11842,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="60" customHeight="1">
       <c r="A150" s="2" t="inlineStr"/>
@@ -10480,6 +11915,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="60" customHeight="1">
       <c r="A151" s="5" t="inlineStr"/>
@@ -10543,6 +11988,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="60" customHeight="1">
       <c r="A152" s="2" t="inlineStr"/>
@@ -10606,6 +12061,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="60" customHeight="1">
       <c r="A153" s="5" t="inlineStr"/>
@@ -10669,6 +12134,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="60" customHeight="1">
       <c r="A154" s="2" t="inlineStr"/>
@@ -10732,6 +12207,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="60" customHeight="1">
       <c r="A155" s="5" t="inlineStr"/>
@@ -10795,6 +12280,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="60" customHeight="1">
       <c r="A156" s="2" t="inlineStr"/>
@@ -10858,6 +12353,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="60" customHeight="1">
       <c r="A157" s="5" t="inlineStr"/>
@@ -10921,6 +12426,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="60" customHeight="1">
       <c r="A158" s="2" t="inlineStr"/>
@@ -10984,6 +12499,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="60" customHeight="1">
       <c r="A159" s="5" t="inlineStr"/>
@@ -11047,6 +12572,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="60" customHeight="1">
       <c r="A160" s="2" t="inlineStr"/>
@@ -11110,6 +12645,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="60" customHeight="1">
       <c r="A161" s="5" t="inlineStr"/>
@@ -11173,6 +12718,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="60" customHeight="1">
       <c r="A162" s="2" t="inlineStr"/>
@@ -11236,6 +12791,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="60" customHeight="1">
       <c r="A163" s="5" t="inlineStr"/>
@@ -11299,6 +12864,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="60" customHeight="1">
       <c r="A164" s="2" t="inlineStr"/>
@@ -11362,6 +12937,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="60" customHeight="1">
       <c r="A165" s="5" t="inlineStr"/>
@@ -11425,6 +13010,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="60" customHeight="1">
       <c r="A166" s="2" t="inlineStr"/>
@@ -11488,6 +13083,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="60" customHeight="1">
       <c r="A167" s="5" t="inlineStr"/>
@@ -11551,6 +13156,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="60" customHeight="1">
       <c r="A168" s="2" t="inlineStr"/>
@@ -11614,6 +13229,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="60" customHeight="1">
       <c r="A169" s="5" t="inlineStr"/>
@@ -11677,6 +13302,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="60" customHeight="1">
       <c r="A170" s="2" t="inlineStr"/>
@@ -11740,6 +13375,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="60" customHeight="1">
       <c r="A171" s="5" t="inlineStr"/>
@@ -11803,6 +13448,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="60" customHeight="1">
       <c r="A172" s="2" t="inlineStr"/>
@@ -11866,6 +13521,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="60" customHeight="1">
       <c r="A173" s="5" t="inlineStr"/>
@@ -11929,6 +13594,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="60" customHeight="1">
       <c r="A174" s="2" t="inlineStr"/>
@@ -11992,6 +13667,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="60" customHeight="1">
       <c r="A175" s="5" t="inlineStr"/>
@@ -12055,6 +13740,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="60" customHeight="1">
       <c r="A176" s="2" t="inlineStr"/>
@@ -12118,6 +13813,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="60" customHeight="1">
       <c r="A177" s="5" t="inlineStr"/>
@@ -12181,6 +13886,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="60" customHeight="1">
       <c r="A178" s="2" t="inlineStr"/>
@@ -12244,6 +13959,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="60" customHeight="1">
       <c r="A179" s="5" t="inlineStr"/>
@@ -12307,6 +14032,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="60" customHeight="1">
       <c r="A180" s="2" t="inlineStr"/>
@@ -12370,6 +14105,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="60" customHeight="1">
       <c r="A181" s="5" t="inlineStr"/>
@@ -12433,6 +14178,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="60" customHeight="1">
       <c r="A182" s="2" t="inlineStr"/>
@@ -12496,6 +14251,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="60" customHeight="1">
       <c r="A183" s="5" t="inlineStr"/>
@@ -12559,6 +14324,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="60" customHeight="1">
       <c r="A184" s="2" t="inlineStr"/>
@@ -12622,6 +14397,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="60" customHeight="1">
       <c r="A185" s="5" t="inlineStr"/>
@@ -12685,6 +14470,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="60" customHeight="1">
       <c r="A186" s="2" t="inlineStr"/>
@@ -12748,6 +14543,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="60" customHeight="1">
       <c r="A187" s="5" t="inlineStr"/>
@@ -12811,6 +14616,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="60" customHeight="1">
       <c r="A188" s="2" t="inlineStr"/>
@@ -12874,6 +14689,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="60" customHeight="1">
       <c r="A189" s="5" t="inlineStr"/>
@@ -12937,6 +14762,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="60" customHeight="1">
       <c r="A190" s="2" t="inlineStr"/>
@@ -13000,6 +14835,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="60" customHeight="1">
       <c r="A191" s="5" t="inlineStr"/>
@@ -13063,6 +14908,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="60" customHeight="1">
       <c r="A192" s="2" t="inlineStr"/>
@@ -13126,6 +14981,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="60" customHeight="1">
       <c r="A193" s="5" t="inlineStr"/>
@@ -13189,6 +15054,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="60" customHeight="1">
       <c r="A194" s="2" t="inlineStr"/>
@@ -13252,6 +15127,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="60" customHeight="1">
       <c r="A195" s="5" t="inlineStr"/>
@@ -13315,6 +15200,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="60" customHeight="1">
       <c r="A196" s="2" t="inlineStr"/>
@@ -13378,6 +15273,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="60" customHeight="1">
       <c r="A197" s="5" t="inlineStr"/>
@@ -13441,6 +15346,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="60" customHeight="1">
       <c r="A198" s="2" t="inlineStr"/>
@@ -13504,6 +15419,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="60" customHeight="1">
       <c r="A199" s="5" t="inlineStr"/>
@@ -13567,6 +15492,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="60" customHeight="1">
       <c r="A200" s="2" t="inlineStr"/>
@@ -13630,6 +15565,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="60" customHeight="1">
       <c r="A201" s="5" t="inlineStr"/>
@@ -13693,6 +15638,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="60" customHeight="1">
       <c r="A202" s="2" t="inlineStr"/>
@@ -13756,6 +15711,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="60" customHeight="1">
       <c r="A203" s="5" t="inlineStr"/>
@@ -13819,6 +15784,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="60" customHeight="1">
       <c r="A204" s="2" t="inlineStr"/>
@@ -13882,6 +15857,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="60" customHeight="1">
       <c r="A205" s="5" t="inlineStr"/>
@@ -13945,6 +15930,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="60" customHeight="1">
       <c r="A206" s="2" t="inlineStr"/>
@@ -14008,6 +16003,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="60" customHeight="1">
       <c r="A207" s="5" t="inlineStr"/>
@@ -14071,6 +16076,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="60" customHeight="1">
       <c r="A208" s="2" t="inlineStr"/>
@@ -14134,6 +16149,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="60" customHeight="1">
       <c r="A209" s="5" t="inlineStr"/>
@@ -14197,6 +16222,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="60" customHeight="1">
       <c r="A210" s="2" t="inlineStr"/>
@@ -14260,6 +16295,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="60" customHeight="1">
       <c r="A211" s="5" t="inlineStr"/>
@@ -14323,6 +16368,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="60" customHeight="1">
       <c r="A212" s="2" t="inlineStr"/>
@@ -14386,6 +16441,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="60" customHeight="1">
       <c r="A213" s="5" t="inlineStr"/>
@@ -14449,6 +16514,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="60" customHeight="1">
       <c r="A214" s="2" t="inlineStr"/>
@@ -14512,6 +16587,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="60" customHeight="1">
       <c r="A215" s="5" t="inlineStr"/>
@@ -14575,6 +16660,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="60" customHeight="1">
       <c r="A216" s="2" t="inlineStr"/>
@@ -14638,6 +16733,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="60" customHeight="1">
       <c r="A217" s="5" t="inlineStr"/>
@@ -14701,6 +16806,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="60" customHeight="1">
       <c r="A218" s="2" t="inlineStr"/>
@@ -14764,6 +16879,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="60" customHeight="1">
       <c r="A219" s="5" t="inlineStr"/>
@@ -14827,6 +16952,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="60" customHeight="1">
       <c r="A220" s="2" t="inlineStr"/>
@@ -14890,6 +17025,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="60" customHeight="1">
       <c r="A221" s="5" t="inlineStr"/>
@@ -14953,6 +17098,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="60" customHeight="1">
       <c r="A222" s="2" t="inlineStr"/>
@@ -15016,6 +17171,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="60" customHeight="1">
       <c r="A223" s="5" t="inlineStr"/>
@@ -15079,6 +17244,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="60" customHeight="1">
       <c r="A224" s="2" t="inlineStr"/>
@@ -15142,6 +17317,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="60" customHeight="1">
       <c r="A225" s="5" t="inlineStr"/>
@@ -15205,6 +17390,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="60" customHeight="1">
       <c r="A226" s="2" t="inlineStr"/>
@@ -15268,6 +17463,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="60" customHeight="1">
       <c r="A227" s="5" t="inlineStr"/>
@@ -15331,6 +17536,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="60" customHeight="1">
       <c r="A228" s="2" t="inlineStr"/>
@@ -15394,6 +17609,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="60" customHeight="1">
       <c r="A229" s="5" t="inlineStr"/>
@@ -15457,6 +17682,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="60" customHeight="1">
       <c r="A230" s="2" t="inlineStr"/>
@@ -15520,6 +17755,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="60" customHeight="1">
       <c r="A231" s="5" t="inlineStr"/>
@@ -15583,6 +17828,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="60" customHeight="1">
       <c r="A232" s="2" t="inlineStr"/>
@@ -15646,6 +17901,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="60" customHeight="1">
       <c r="A233" s="5" t="inlineStr"/>
@@ -15709,6 +17974,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="60" customHeight="1">
       <c r="A234" s="2" t="inlineStr"/>
@@ -15772,6 +18047,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="60" customHeight="1">
       <c r="A235" s="5" t="inlineStr"/>
@@ -15835,6 +18120,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="60" customHeight="1">
       <c r="A236" s="2" t="inlineStr"/>
@@ -15898,6 +18193,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="60" customHeight="1">
       <c r="A237" s="5" t="inlineStr"/>
@@ -15961,6 +18266,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="60" customHeight="1">
       <c r="A238" s="2" t="inlineStr"/>
@@ -16024,6 +18339,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="60" customHeight="1">
       <c r="A239" s="5" t="inlineStr"/>
@@ -16087,6 +18412,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="60" customHeight="1">
       <c r="A240" s="2" t="inlineStr"/>
@@ -16150,6 +18485,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="60" customHeight="1">
       <c r="A241" s="5" t="inlineStr"/>
@@ -16213,6 +18558,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="60" customHeight="1">
       <c r="A242" s="2" t="inlineStr"/>
@@ -16276,6 +18631,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="60" customHeight="1">
       <c r="A243" s="5" t="inlineStr"/>
@@ -16339,6 +18704,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="60" customHeight="1">
       <c r="A244" s="2" t="inlineStr"/>
@@ -16402,6 +18777,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="60" customHeight="1">
       <c r="A245" s="5" t="inlineStr"/>
@@ -16465,6 +18850,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="60" customHeight="1">
       <c r="A246" s="2" t="inlineStr"/>
@@ -16528,6 +18923,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="60" customHeight="1">
       <c r="A247" s="5" t="inlineStr"/>
@@ -16591,6 +18996,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="60" customHeight="1">
       <c r="A248" s="2" t="inlineStr"/>
@@ -16654,6 +19069,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="60" customHeight="1">
       <c r="A249" s="5" t="inlineStr"/>
@@ -16717,6 +19142,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="60" customHeight="1">
       <c r="A250" s="2" t="inlineStr"/>
@@ -16780,6 +19215,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="60" customHeight="1">
       <c r="A251" s="5" t="inlineStr"/>
@@ -16843,6 +19288,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="60" customHeight="1">
       <c r="A252" s="2" t="inlineStr"/>
@@ -16906,6 +19361,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="60" customHeight="1">
       <c r="A253" s="5" t="inlineStr"/>
@@ -16969,6 +19434,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="60" customHeight="1">
       <c r="A254" s="2" t="inlineStr"/>
@@ -17032,6 +19507,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="60" customHeight="1">
       <c r="A255" s="5" t="inlineStr"/>
@@ -17095,6 +19580,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="60" customHeight="1">
       <c r="A256" s="2" t="inlineStr"/>
@@ -17158,6 +19653,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="60" customHeight="1">
       <c r="A257" s="5" t="inlineStr"/>
@@ -17221,6 +19726,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="60" customHeight="1">
       <c r="A258" s="2" t="inlineStr"/>
@@ -17284,6 +19799,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="60" customHeight="1">
       <c r="A259" s="5" t="inlineStr"/>
@@ -17347,6 +19872,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="60" customHeight="1">
       <c r="A260" s="2" t="inlineStr"/>
@@ -17410,6 +19945,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="60" customHeight="1">
       <c r="A261" s="5" t="inlineStr"/>
@@ -17473,6 +20018,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="60" customHeight="1">
       <c r="A262" s="2" t="inlineStr"/>
@@ -17536,6 +20091,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="60" customHeight="1">
       <c r="A263" s="5" t="inlineStr"/>
@@ -17599,6 +20164,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="60" customHeight="1">
       <c r="A264" s="2" t="inlineStr"/>
@@ -17662,6 +20237,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="60" customHeight="1">
       <c r="A265" s="5" t="inlineStr"/>
@@ -17725,6 +20310,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="60" customHeight="1">
       <c r="A266" s="2" t="inlineStr"/>
@@ -17788,6 +20383,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="60" customHeight="1">
       <c r="A267" s="5" t="inlineStr"/>
@@ -17851,6 +20456,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="60" customHeight="1">
       <c r="A268" s="2" t="inlineStr"/>
@@ -17914,6 +20529,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="60" customHeight="1">
       <c r="A269" s="5" t="inlineStr"/>
@@ -17977,6 +20602,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="60" customHeight="1">
       <c r="A270" s="2" t="inlineStr"/>
@@ -18040,6 +20675,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="60" customHeight="1">
       <c r="A271" s="5" t="inlineStr"/>
@@ -18103,6 +20748,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="60" customHeight="1">
       <c r="A272" s="2" t="inlineStr"/>
@@ -18166,6 +20821,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="60" customHeight="1">
       <c r="A273" s="5" t="inlineStr"/>
@@ -18229,6 +20894,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="60" customHeight="1">
       <c r="A274" s="2" t="inlineStr"/>
@@ -18292,6 +20967,16 @@
           <t>Spurious guard removed in wave-1-low-complexity-fixes branch</t>
         </is>
       </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>Phase 2 static</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -18324,7 +21009,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Wave 1</t>
+          <t>Phase 2 / Wave 1 guard test</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -18357,6 +21042,12 @@
           <t>sys_hub_flow_trigger is not a writable ServiceNow table. Flow triggering requires the Flow Designer API.</t>
         </is>
       </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>Wave 1 guard test</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -18389,7 +21080,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Wave 1</t>
+          <t>Phase 2 / Wave 1 guard test</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -18422,6 +21113,12 @@
           <t>sys_hub_subflow is not a ServiceNow table. Both list and get must filter sys_hub_flow by type=subflow.</t>
         </is>
       </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>Wave 1 guard test</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -18454,7 +21151,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Wave 1</t>
+          <t>Phase 2 / Wave 1 guard test</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -18487,6 +21184,12 @@
           <t>50 records returned when filtering by newly-created portal; expected 0. Filter field name mismatch suspected.</t>
         </is>
       </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>Wave 1 guard test</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -18519,7 +21222,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Wave 1</t>
+          <t>Phase 2 / Wave 1 guard test</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -18552,6 +21255,12 @@
           <t>22 records returned when filtering by fake app_sys_id; expected 0. Filter field likely wrong.</t>
         </is>
       </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>Wave 1 guard test</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -18584,7 +21293,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Wave 1</t>
+          <t>Phase 2 / Wave 1 guard test</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -18617,6 +21326,12 @@
           <t>sysevent_register uses event_name as the primary identifier, not name. Query with name= silently ignores filter.</t>
         </is>
       </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>Wave 1 guard test</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -18649,7 +21364,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Wave 1</t>
+          <t>Phase 2 / Wave 1 guard test</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18682,6 +21397,12 @@
           <t>Record sys_id 0cafcb3b83e40310ad3cc4d0deaad3c9 created with empty event_name. Cleanup required on PDI.</t>
         </is>
       </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>Wave 1 guard test</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -18714,7 +21435,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Wave 1</t>
+          <t>Phase 2 / Wave 1 guard test</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18747,6 +21468,12 @@
           <t>sys_ui_hp is not a ServiceNow table. Standard homepages are in sys_ui_homepage.</t>
         </is>
       </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>Wave 1 guard test</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -18779,7 +21506,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Wave 1</t>
+          <t>Phase 2 / Wave 1 guard test</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18812,6 +21539,12 @@
           <t>pa_job does not exist on standard ServiceNow instances. Confirmed INVALID_REQUEST on PDI.</t>
         </is>
       </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>Wave 1 guard test</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -18844,7 +21577,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Wave 1</t>
+          <t>Phase 2 / Wave 1 guard test</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18877,6 +21610,12 @@
           <t>PDI may have uncategorised properties only, making this hard to isolate. Verify on production-like instance.</t>
         </is>
       </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>Wave 1 guard test</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -18909,7 +21648,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Wave 1</t>
+          <t>Phase 2 / Wave 1 guard test</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18942,6 +21681,12 @@
           <t>sys_cs_conversation_message is not a standard table. Correct table may require Conversational Platform license.</t>
         </is>
       </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>Wave 1 guard test</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -18974,7 +21719,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Wave 1</t>
+          <t>Phase 2 / Wave 1 guard test</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -19007,6 +21752,12 @@
           <t>sys_cs_category is not a standard ServiceNow table. Category data may be stored differently in newer VA versions.</t>
         </is>
       </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>Wave 1 guard test</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -19039,7 +21790,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Wave 1</t>
+          <t>Phase 2 / Wave 1 guard test</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -19072,6 +21823,12 @@
           <t>Tool tries /api/now/pa/widget/ first; on error falls back to pa_job_log which does not exist. pa_job_log is not a standard table.</t>
         </is>
       </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>Wave 1 guard test</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -19104,7 +21861,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Wave 1</t>
+          <t>Phase 2 / Wave 1 guard test</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -19137,6 +21894,12 @@
           <t>ml_solution_version is not a standard ServiceNow table. Training history may be in ml_solution or a plugin-specific table.</t>
         </is>
       </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>Wave 1 guard test</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M274"/>
@@ -19145,6 +21908,159 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="55" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>Wave</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>Date Merged</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t>Tools Tested</t>
+        </is>
+      </c>
+      <c r="F1" s="20" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G1" s="20" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="H1" s="20" t="inlineStr">
+        <is>
+          <t>Fishy</t>
+        </is>
+      </c>
+      <c r="I1" s="20" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="J1" s="20" t="inlineStr">
+        <is>
+          <t>Issue # Range</t>
+        </is>
+      </c>
+      <c r="K1" s="20" t="inlineStr">
+        <is>
+          <t>Fix Applied</t>
+        </is>
+      </c>
+      <c r="L1" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="M1" s="20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>wave-1-low-complexity-fixes</t>
+        </is>
+      </c>
+      <c r="C2" s="21" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="inlineStr">
+        <is>
+          <t>20 Category B handler files + reporting.ts (21 files total)</t>
+        </is>
+      </c>
+      <c r="E2" s="21" t="n">
+        <v>272</v>
+      </c>
+      <c r="F2" s="21" t="n">
+        <v>216</v>
+      </c>
+      <c r="G2" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H2" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="J2" s="21" t="inlineStr">
+        <is>
+          <t>#9 (fixed), #13–25 (escalated)</t>
+        </is>
+      </c>
+      <c r="K2" s="21" t="inlineStr">
+        <is>
+          <t>Single NOW_ASSIST guard bug fixed in dispatcher; table fixes for #7, #8, #9</t>
+        </is>
+      </c>
+      <c r="L2" s="21" t="inlineStr">
+        <is>
+          <t>Merged</t>
+        </is>
+      </c>
+      <c r="M2" s="21" t="inlineStr">
+        <is>
+          <t>Skips: HRSD 16, Mobile 8, DevOps 6, Agent Workspace 3, SecOps-partial 3, PAD 2. 28 PDI test records logged for cleanup.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
